--- a/data/experiment2_final_choice_conflict_proportions.xlsx
+++ b/data/experiment2_final_choice_conflict_proportions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marta\Nextcloud\Shared_SweetC\Experiments\ExpPrefer\GitHub\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5DA6FB7-7D72-45D9-BF63-472ABEAAC3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D341186B-E1E2-45AC-960D-8414CE4F565F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ConflictProportionFinalSliderID" sheetId="1" r:id="rId1"/>
@@ -35,9 +35,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="8">
   <si>
-    <t>Participant Private ID</t>
-  </si>
-  <si>
     <t>Conflict_Level</t>
   </si>
   <si>
@@ -57,6 +54,9 @@
   </si>
   <si>
     <t>Stroop</t>
+  </si>
+  <si>
+    <t>Participant</t>
   </si>
 </sst>
 </file>
@@ -115,12 +115,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -436,16 +433,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>6</v>
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
@@ -453,13 +450,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -467,13 +464,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -481,13 +478,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -495,13 +492,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -509,13 +506,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -523,13 +520,13 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -537,13 +534,13 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -551,13 +548,13 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9">
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
@@ -565,13 +562,13 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -579,13 +576,13 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11">
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -593,13 +590,13 @@
         <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -607,13 +604,13 @@
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -621,13 +618,13 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -635,13 +632,13 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -649,13 +646,13 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -663,13 +660,13 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -677,13 +674,13 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -691,13 +688,13 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -705,13 +702,13 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -719,13 +716,13 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -733,13 +730,13 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -747,13 +744,13 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -761,13 +758,13 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -775,13 +772,13 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -789,13 +786,13 @@
         <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -803,13 +800,13 @@
         <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -817,13 +814,13 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C28">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -831,13 +828,13 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -845,13 +842,13 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -859,13 +856,13 @@
         <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -873,13 +870,13 @@
         <v>11</v>
       </c>
       <c r="B32" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -887,13 +884,13 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -901,13 +898,13 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34">
         <v>1</v>
       </c>
       <c r="D34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -915,13 +912,13 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -929,13 +926,13 @@
         <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -943,13 +940,13 @@
         <v>12</v>
       </c>
       <c r="B37" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -957,13 +954,13 @@
         <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -971,13 +968,13 @@
         <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
@@ -985,13 +982,13 @@
         <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40">
         <v>1</v>
       </c>
       <c r="D40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -999,13 +996,13 @@
         <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41">
         <v>1</v>
       </c>
       <c r="D41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -1013,13 +1010,13 @@
         <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -1027,13 +1024,13 @@
         <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -1041,13 +1038,13 @@
         <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -1055,13 +1052,13 @@
         <v>15</v>
       </c>
       <c r="B45" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -1069,13 +1066,13 @@
         <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -1083,13 +1080,13 @@
         <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C47">
         <v>1</v>
       </c>
       <c r="D47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -1097,13 +1094,13 @@
         <v>16</v>
       </c>
       <c r="B48" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -1111,13 +1108,13 @@
         <v>16</v>
       </c>
       <c r="B49" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -1125,13 +1122,13 @@
         <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -1139,13 +1136,13 @@
         <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C51">
         <v>1</v>
       </c>
       <c r="D51" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -1153,13 +1150,13 @@
         <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -1167,13 +1164,13 @@
         <v>18</v>
       </c>
       <c r="B53" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -1181,13 +1178,13 @@
         <v>18</v>
       </c>
       <c r="B54" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
@@ -1195,13 +1192,13 @@
         <v>18</v>
       </c>
       <c r="B55" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -1209,13 +1206,13 @@
         <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
@@ -1223,13 +1220,13 @@
         <v>19</v>
       </c>
       <c r="B57" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>1</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -1237,13 +1234,13 @@
         <v>19</v>
       </c>
       <c r="B58" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
@@ -1251,13 +1248,13 @@
         <v>20</v>
       </c>
       <c r="B59" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59">
         <v>1</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -1265,13 +1262,13 @@
         <v>20</v>
       </c>
       <c r="B60" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -1279,13 +1276,13 @@
         <v>20</v>
       </c>
       <c r="B61" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -1293,13 +1290,13 @@
         <v>21</v>
       </c>
       <c r="B62" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
@@ -1307,13 +1304,13 @@
         <v>21</v>
       </c>
       <c r="B63" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
@@ -1321,13 +1318,13 @@
         <v>21</v>
       </c>
       <c r="B64" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
@@ -1335,13 +1332,13 @@
         <v>22</v>
       </c>
       <c r="B65" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
@@ -1349,13 +1346,13 @@
         <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66">
         <v>1</v>
       </c>
       <c r="D66" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
@@ -1363,13 +1360,13 @@
         <v>22</v>
       </c>
       <c r="B67" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
@@ -1377,13 +1374,13 @@
         <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
@@ -1391,13 +1388,13 @@
         <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
@@ -1405,13 +1402,13 @@
         <v>23</v>
       </c>
       <c r="B70" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
@@ -1419,13 +1416,13 @@
         <v>24</v>
       </c>
       <c r="B71" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
         <v>1</v>
       </c>
       <c r="D71" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
@@ -1433,13 +1430,13 @@
         <v>24</v>
       </c>
       <c r="B72" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
@@ -1447,13 +1444,13 @@
         <v>24</v>
       </c>
       <c r="B73" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
@@ -1461,13 +1458,13 @@
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
@@ -1475,13 +1472,13 @@
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
@@ -1489,13 +1486,13 @@
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C76">
         <v>1</v>
       </c>
       <c r="D76" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
@@ -1503,13 +1500,13 @@
         <v>26</v>
       </c>
       <c r="B77" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
@@ -1517,13 +1514,13 @@
         <v>26</v>
       </c>
       <c r="B78" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
@@ -1531,13 +1528,13 @@
         <v>26</v>
       </c>
       <c r="B79" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C79">
         <v>1</v>
       </c>
       <c r="D79" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
@@ -1545,13 +1542,13 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80">
         <v>1</v>
       </c>
       <c r="D80" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
@@ -1559,13 +1556,13 @@
         <v>27</v>
       </c>
       <c r="B81" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
@@ -1573,13 +1570,13 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
@@ -1587,13 +1584,13 @@
         <v>28</v>
       </c>
       <c r="B83" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
@@ -1601,13 +1598,13 @@
         <v>28</v>
       </c>
       <c r="B84" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
@@ -1615,13 +1612,13 @@
         <v>28</v>
       </c>
       <c r="B85" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C85">
         <v>1</v>
       </c>
       <c r="D85" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
@@ -1629,13 +1626,13 @@
         <v>29</v>
       </c>
       <c r="B86" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C86">
         <v>1</v>
       </c>
       <c r="D86" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
@@ -1643,13 +1640,13 @@
         <v>29</v>
       </c>
       <c r="B87" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
@@ -1657,13 +1654,13 @@
         <v>29</v>
       </c>
       <c r="B88" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
@@ -1671,13 +1668,13 @@
         <v>30</v>
       </c>
       <c r="B89" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
@@ -1685,13 +1682,13 @@
         <v>30</v>
       </c>
       <c r="B90" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
@@ -1699,13 +1696,13 @@
         <v>30</v>
       </c>
       <c r="B91" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C91">
         <v>1</v>
       </c>
       <c r="D91" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
@@ -1713,13 +1710,13 @@
         <v>31</v>
       </c>
       <c r="B92" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92">
         <v>1</v>
       </c>
       <c r="D92" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
@@ -1727,13 +1724,13 @@
         <v>31</v>
       </c>
       <c r="B93" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
@@ -1741,13 +1738,13 @@
         <v>31</v>
       </c>
       <c r="B94" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
@@ -1755,13 +1752,13 @@
         <v>32</v>
       </c>
       <c r="B95" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
@@ -1769,13 +1766,13 @@
         <v>32</v>
       </c>
       <c r="B96" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
@@ -1783,13 +1780,13 @@
         <v>32</v>
       </c>
       <c r="B97" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C97">
         <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
@@ -1797,13 +1794,13 @@
         <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
@@ -1811,13 +1808,13 @@
         <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
@@ -1825,13 +1822,13 @@
         <v>33</v>
       </c>
       <c r="B100" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C100">
         <v>1</v>
       </c>
       <c r="D100" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
@@ -1839,13 +1836,13 @@
         <v>34</v>
       </c>
       <c r="B101" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C101">
         <v>1</v>
       </c>
       <c r="D101" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
@@ -1853,13 +1850,13 @@
         <v>34</v>
       </c>
       <c r="B102" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
@@ -1867,13 +1864,13 @@
         <v>34</v>
       </c>
       <c r="B103" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
@@ -1881,13 +1878,13 @@
         <v>35</v>
       </c>
       <c r="B104" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C104">
         <v>1</v>
       </c>
       <c r="D104" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
@@ -1895,13 +1892,13 @@
         <v>35</v>
       </c>
       <c r="B105" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C105">
         <v>0</v>
       </c>
       <c r="D105" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
@@ -1909,13 +1906,13 @@
         <v>35</v>
       </c>
       <c r="B106" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C106">
         <v>0</v>
       </c>
       <c r="D106" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
@@ -1923,13 +1920,13 @@
         <v>36</v>
       </c>
       <c r="B107" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C107">
         <v>0</v>
       </c>
       <c r="D107" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
@@ -1937,13 +1934,13 @@
         <v>36</v>
       </c>
       <c r="B108" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C108">
         <v>0</v>
       </c>
       <c r="D108" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
@@ -1951,13 +1948,13 @@
         <v>36</v>
       </c>
       <c r="B109" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C109">
         <v>1</v>
       </c>
       <c r="D109" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
@@ -1965,13 +1962,13 @@
         <v>37</v>
       </c>
       <c r="B110" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C110">
         <v>0</v>
       </c>
       <c r="D110" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
@@ -1979,13 +1976,13 @@
         <v>37</v>
       </c>
       <c r="B111" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
@@ -1993,13 +1990,13 @@
         <v>37</v>
       </c>
       <c r="B112" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C112">
         <v>1</v>
       </c>
       <c r="D112" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
@@ -2007,13 +2004,13 @@
         <v>38</v>
       </c>
       <c r="B113" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113">
         <v>1</v>
       </c>
       <c r="D113" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
@@ -2021,13 +2018,13 @@
         <v>38</v>
       </c>
       <c r="B114" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
@@ -2035,13 +2032,13 @@
         <v>38</v>
       </c>
       <c r="B115" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
@@ -2049,13 +2046,13 @@
         <v>39</v>
       </c>
       <c r="B116" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C116">
         <v>0</v>
       </c>
       <c r="D116" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
@@ -2063,13 +2060,13 @@
         <v>39</v>
       </c>
       <c r="B117" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C117">
         <v>1</v>
       </c>
       <c r="D117" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
@@ -2077,13 +2074,13 @@
         <v>39</v>
       </c>
       <c r="B118" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C118">
         <v>0</v>
       </c>
       <c r="D118" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
@@ -2091,13 +2088,13 @@
         <v>40</v>
       </c>
       <c r="B119" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C119">
         <v>0</v>
       </c>
       <c r="D119" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
@@ -2105,13 +2102,13 @@
         <v>40</v>
       </c>
       <c r="B120" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C120">
         <v>0</v>
       </c>
       <c r="D120" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
@@ -2119,13 +2116,13 @@
         <v>40</v>
       </c>
       <c r="B121" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C121">
         <v>1</v>
       </c>
       <c r="D121" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
@@ -2133,13 +2130,13 @@
         <v>41</v>
       </c>
       <c r="B122" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C122">
         <v>0</v>
       </c>
       <c r="D122" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
@@ -2147,13 +2144,13 @@
         <v>41</v>
       </c>
       <c r="B123" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C123">
         <v>0</v>
       </c>
       <c r="D123" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
@@ -2161,13 +2158,13 @@
         <v>41</v>
       </c>
       <c r="B124" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C124">
         <v>1</v>
       </c>
       <c r="D124" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
@@ -2175,13 +2172,13 @@
         <v>42</v>
       </c>
       <c r="B125" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C125">
         <v>1</v>
       </c>
       <c r="D125" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
@@ -2189,13 +2186,13 @@
         <v>42</v>
       </c>
       <c r="B126" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C126">
         <v>0</v>
       </c>
       <c r="D126" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
@@ -2203,13 +2200,13 @@
         <v>42</v>
       </c>
       <c r="B127" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C127">
         <v>0</v>
       </c>
       <c r="D127" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
@@ -2217,13 +2214,13 @@
         <v>43</v>
       </c>
       <c r="B128" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C128">
         <v>0</v>
       </c>
       <c r="D128" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
@@ -2231,13 +2228,13 @@
         <v>43</v>
       </c>
       <c r="B129" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C129">
         <v>1</v>
       </c>
       <c r="D129" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
@@ -2245,13 +2242,13 @@
         <v>43</v>
       </c>
       <c r="B130" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C130">
         <v>0</v>
       </c>
       <c r="D130" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
@@ -2259,13 +2256,13 @@
         <v>44</v>
       </c>
       <c r="B131" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C131">
         <v>0</v>
       </c>
       <c r="D131" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
@@ -2273,13 +2270,13 @@
         <v>44</v>
       </c>
       <c r="B132" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C132">
         <v>1</v>
       </c>
       <c r="D132" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
@@ -2287,13 +2284,13 @@
         <v>44</v>
       </c>
       <c r="B133" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C133">
         <v>0</v>
       </c>
       <c r="D133" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
@@ -2301,13 +2298,13 @@
         <v>45</v>
       </c>
       <c r="B134" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C134">
         <v>1</v>
       </c>
       <c r="D134" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
@@ -2315,13 +2312,13 @@
         <v>45</v>
       </c>
       <c r="B135" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C135">
         <v>0</v>
       </c>
       <c r="D135" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
@@ -2329,13 +2326,13 @@
         <v>45</v>
       </c>
       <c r="B136" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C136">
         <v>0</v>
       </c>
       <c r="D136" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
@@ -2343,13 +2340,13 @@
         <v>46</v>
       </c>
       <c r="B137" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C137">
         <v>0</v>
       </c>
       <c r="D137" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
@@ -2357,13 +2354,13 @@
         <v>46</v>
       </c>
       <c r="B138" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C138">
         <v>1</v>
       </c>
       <c r="D138" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
@@ -2371,13 +2368,13 @@
         <v>46</v>
       </c>
       <c r="B139" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C139">
         <v>0</v>
       </c>
       <c r="D139" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
@@ -2385,13 +2382,13 @@
         <v>47</v>
       </c>
       <c r="B140" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C140">
         <v>0</v>
       </c>
       <c r="D140" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
@@ -2399,13 +2396,13 @@
         <v>47</v>
       </c>
       <c r="B141" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C141">
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
@@ -2413,13 +2410,13 @@
         <v>47</v>
       </c>
       <c r="B142" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C142">
         <v>0</v>
       </c>
       <c r="D142" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
@@ -2427,13 +2424,13 @@
         <v>48</v>
       </c>
       <c r="B143" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C143">
         <v>0</v>
       </c>
       <c r="D143" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
@@ -2441,13 +2438,13 @@
         <v>48</v>
       </c>
       <c r="B144" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C144">
         <v>0</v>
       </c>
       <c r="D144" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
@@ -2455,13 +2452,13 @@
         <v>48</v>
       </c>
       <c r="B145" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C145">
         <v>1</v>
       </c>
       <c r="D145" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
@@ -2469,13 +2466,13 @@
         <v>49</v>
       </c>
       <c r="B146" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
       <c r="D146" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
@@ -2483,13 +2480,13 @@
         <v>49</v>
       </c>
       <c r="B147" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C147">
         <v>0</v>
       </c>
       <c r="D147" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
@@ -2497,13 +2494,13 @@
         <v>49</v>
       </c>
       <c r="B148" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C148">
         <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
@@ -2511,13 +2508,13 @@
         <v>50</v>
       </c>
       <c r="B149" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C149">
         <v>0</v>
       </c>
       <c r="D149" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
@@ -2525,13 +2522,13 @@
         <v>50</v>
       </c>
       <c r="B150" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="D150" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
@@ -2539,13 +2536,13 @@
         <v>50</v>
       </c>
       <c r="B151" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C151">
         <v>0</v>
       </c>
       <c r="D151" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
@@ -2553,13 +2550,13 @@
         <v>51</v>
       </c>
       <c r="B152" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C152">
         <v>1</v>
       </c>
       <c r="D152" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
@@ -2567,13 +2564,13 @@
         <v>51</v>
       </c>
       <c r="B153" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C153">
         <v>0</v>
       </c>
       <c r="D153" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
@@ -2581,13 +2578,13 @@
         <v>51</v>
       </c>
       <c r="B154" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C154">
         <v>0</v>
       </c>
       <c r="D154" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
@@ -2595,13 +2592,13 @@
         <v>52</v>
       </c>
       <c r="B155" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C155">
         <v>0</v>
       </c>
       <c r="D155" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
@@ -2609,13 +2606,13 @@
         <v>52</v>
       </c>
       <c r="B156" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C156">
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
@@ -2623,13 +2620,13 @@
         <v>52</v>
       </c>
       <c r="B157" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
@@ -2637,13 +2634,13 @@
         <v>53</v>
       </c>
       <c r="B158" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C158">
         <v>0</v>
       </c>
       <c r="D158" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
@@ -2651,13 +2648,13 @@
         <v>53</v>
       </c>
       <c r="B159" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C159">
         <v>0</v>
       </c>
       <c r="D159" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.35">
@@ -2665,13 +2662,13 @@
         <v>53</v>
       </c>
       <c r="B160" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C160">
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
@@ -2679,13 +2676,13 @@
         <v>54</v>
       </c>
       <c r="B161" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C161">
         <v>0</v>
       </c>
       <c r="D161" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.35">
@@ -2693,13 +2690,13 @@
         <v>54</v>
       </c>
       <c r="B162" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C162">
         <v>0</v>
       </c>
       <c r="D162" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.35">
@@ -2707,13 +2704,13 @@
         <v>54</v>
       </c>
       <c r="B163" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C163">
         <v>1</v>
       </c>
       <c r="D163" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.35">
@@ -2721,13 +2718,13 @@
         <v>55</v>
       </c>
       <c r="B164" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C164">
         <v>0</v>
       </c>
       <c r="D164" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.35">
@@ -2735,13 +2732,13 @@
         <v>55</v>
       </c>
       <c r="B165" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C165">
         <v>1</v>
       </c>
       <c r="D165" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.35">
@@ -2749,13 +2746,13 @@
         <v>55</v>
       </c>
       <c r="B166" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C166">
         <v>0</v>
       </c>
       <c r="D166" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.35">
@@ -2763,13 +2760,13 @@
         <v>56</v>
       </c>
       <c r="B167" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C167">
         <v>0</v>
       </c>
       <c r="D167" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.35">
@@ -2777,13 +2774,13 @@
         <v>56</v>
       </c>
       <c r="B168" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C168">
         <v>1</v>
       </c>
       <c r="D168" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.35">
@@ -2791,13 +2788,13 @@
         <v>56</v>
       </c>
       <c r="B169" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C169">
         <v>0</v>
       </c>
       <c r="D169" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.35">
@@ -2805,13 +2802,13 @@
         <v>57</v>
       </c>
       <c r="B170" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C170">
         <v>1</v>
       </c>
       <c r="D170" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.35">
@@ -2819,13 +2816,13 @@
         <v>57</v>
       </c>
       <c r="B171" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C171">
         <v>0</v>
       </c>
       <c r="D171" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.35">
@@ -2833,13 +2830,13 @@
         <v>57</v>
       </c>
       <c r="B172" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C172">
         <v>0</v>
       </c>
       <c r="D172" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.35">
@@ -2847,13 +2844,13 @@
         <v>58</v>
       </c>
       <c r="B173" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.35">
@@ -2861,13 +2858,13 @@
         <v>58</v>
       </c>
       <c r="B174" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C174">
         <v>0</v>
       </c>
       <c r="D174" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.35">
@@ -2875,13 +2872,13 @@
         <v>58</v>
       </c>
       <c r="B175" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C175">
         <v>0</v>
       </c>
       <c r="D175" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.35">
@@ -2889,13 +2886,13 @@
         <v>59</v>
       </c>
       <c r="B176" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="D176" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.35">
@@ -2903,13 +2900,13 @@
         <v>59</v>
       </c>
       <c r="B177" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C177">
         <v>0</v>
       </c>
       <c r="D177" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.35">
@@ -2917,13 +2914,13 @@
         <v>59</v>
       </c>
       <c r="B178" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C178">
         <v>0</v>
       </c>
       <c r="D178" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.35">
@@ -2931,13 +2928,13 @@
         <v>60</v>
       </c>
       <c r="B179" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C179">
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.35">
@@ -2945,13 +2942,13 @@
         <v>60</v>
       </c>
       <c r="B180" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C180">
         <v>0</v>
       </c>
       <c r="D180" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.35">
@@ -2959,13 +2956,13 @@
         <v>60</v>
       </c>
       <c r="B181" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C181">
         <v>0</v>
       </c>
       <c r="D181" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.35">
@@ -2973,13 +2970,13 @@
         <v>61</v>
       </c>
       <c r="B182" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="D182" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.35">
@@ -2987,13 +2984,13 @@
         <v>61</v>
       </c>
       <c r="B183" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C183">
         <v>0</v>
       </c>
       <c r="D183" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.35">
@@ -3001,13 +2998,13 @@
         <v>61</v>
       </c>
       <c r="B184" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C184">
         <v>0</v>
       </c>
       <c r="D184" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.35">
@@ -3015,13 +3012,13 @@
         <v>62</v>
       </c>
       <c r="B185" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C185">
         <v>0</v>
       </c>
       <c r="D185" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.35">
@@ -3029,13 +3026,13 @@
         <v>62</v>
       </c>
       <c r="B186" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C186">
         <v>0</v>
       </c>
       <c r="D186" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.35">
@@ -3043,13 +3040,13 @@
         <v>62</v>
       </c>
       <c r="B187" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.35">
@@ -3057,13 +3054,13 @@
         <v>63</v>
       </c>
       <c r="B188" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.35">
@@ -3071,13 +3068,13 @@
         <v>63</v>
       </c>
       <c r="B189" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C189">
         <v>0</v>
       </c>
       <c r="D189" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.35">
@@ -3085,13 +3082,13 @@
         <v>63</v>
       </c>
       <c r="B190" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C190">
         <v>0</v>
       </c>
       <c r="D190" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.35">
@@ -3099,13 +3096,13 @@
         <v>64</v>
       </c>
       <c r="B191" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.35">
@@ -3113,13 +3110,13 @@
         <v>64</v>
       </c>
       <c r="B192" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C192">
         <v>0</v>
       </c>
       <c r="D192" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.35">
@@ -3127,13 +3124,13 @@
         <v>64</v>
       </c>
       <c r="B193" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C193">
         <v>0</v>
       </c>
       <c r="D193" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.35">
@@ -3141,13 +3138,13 @@
         <v>65</v>
       </c>
       <c r="B194" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.35">
@@ -3155,13 +3152,13 @@
         <v>65</v>
       </c>
       <c r="B195" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C195">
         <v>0</v>
       </c>
       <c r="D195" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.35">
@@ -3169,13 +3166,13 @@
         <v>65</v>
       </c>
       <c r="B196" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C196">
         <v>0</v>
       </c>
       <c r="D196" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.35">
@@ -3183,13 +3180,13 @@
         <v>66</v>
       </c>
       <c r="B197" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C197">
         <v>0</v>
       </c>
       <c r="D197" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.35">
@@ -3197,13 +3194,13 @@
         <v>66</v>
       </c>
       <c r="B198" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C198">
         <v>0</v>
       </c>
       <c r="D198" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.35">
@@ -3211,13 +3208,13 @@
         <v>66</v>
       </c>
       <c r="B199" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.35">
@@ -3225,13 +3222,13 @@
         <v>67</v>
       </c>
       <c r="B200" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.35">
@@ -3239,13 +3236,13 @@
         <v>67</v>
       </c>
       <c r="B201" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C201">
         <v>0</v>
       </c>
       <c r="D201" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.35">
@@ -3253,13 +3250,13 @@
         <v>67</v>
       </c>
       <c r="B202" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C202">
         <v>0</v>
       </c>
       <c r="D202" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.35">
@@ -3267,13 +3264,13 @@
         <v>68</v>
       </c>
       <c r="B203" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C203">
         <v>0</v>
       </c>
       <c r="D203" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.35">
@@ -3281,13 +3278,13 @@
         <v>68</v>
       </c>
       <c r="B204" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.35">
@@ -3295,13 +3292,13 @@
         <v>68</v>
       </c>
       <c r="B205" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C205">
         <v>0</v>
       </c>
       <c r="D205" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.35">
@@ -3309,13 +3306,13 @@
         <v>69</v>
       </c>
       <c r="B206" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C206">
         <v>0</v>
       </c>
       <c r="D206" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.35">
@@ -3323,13 +3320,13 @@
         <v>69</v>
       </c>
       <c r="B207" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C207">
         <v>0</v>
       </c>
       <c r="D207" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.35">
@@ -3337,13 +3334,13 @@
         <v>69</v>
       </c>
       <c r="B208" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.35">
@@ -3351,13 +3348,13 @@
         <v>70</v>
       </c>
       <c r="B209" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.35">
@@ -3365,13 +3362,13 @@
         <v>70</v>
       </c>
       <c r="B210" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C210">
         <v>0</v>
       </c>
       <c r="D210" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.35">
@@ -3379,13 +3376,13 @@
         <v>70</v>
       </c>
       <c r="B211" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C211">
         <v>0</v>
       </c>
       <c r="D211" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.35">
@@ -3393,13 +3390,13 @@
         <v>71</v>
       </c>
       <c r="B212" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.35">
@@ -3407,13 +3404,13 @@
         <v>71</v>
       </c>
       <c r="B213" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C213">
         <v>0</v>
       </c>
       <c r="D213" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.35">
@@ -3421,13 +3418,13 @@
         <v>71</v>
       </c>
       <c r="B214" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C214">
         <v>0</v>
       </c>
       <c r="D214" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.35">
@@ -3435,13 +3432,13 @@
         <v>72</v>
       </c>
       <c r="B215" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C215">
         <v>0</v>
       </c>
       <c r="D215" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.35">
@@ -3449,13 +3446,13 @@
         <v>72</v>
       </c>
       <c r="B216" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C216">
         <v>0</v>
       </c>
       <c r="D216" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.35">
@@ -3463,13 +3460,13 @@
         <v>72</v>
       </c>
       <c r="B217" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C217">
         <v>1</v>
       </c>
       <c r="D217" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.35">
@@ -3477,13 +3474,13 @@
         <v>73</v>
       </c>
       <c r="B218" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C218">
         <v>0</v>
       </c>
       <c r="D218" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.35">
@@ -3491,13 +3488,13 @@
         <v>73</v>
       </c>
       <c r="B219" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C219">
         <v>0</v>
       </c>
       <c r="D219" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.35">
@@ -3505,13 +3502,13 @@
         <v>73</v>
       </c>
       <c r="B220" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.35">
@@ -3519,13 +3516,13 @@
         <v>74</v>
       </c>
       <c r="B221" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C221">
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.35">
@@ -3533,13 +3530,13 @@
         <v>74</v>
       </c>
       <c r="B222" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C222">
         <v>0</v>
       </c>
       <c r="D222" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.35">
@@ -3547,13 +3544,13 @@
         <v>74</v>
       </c>
       <c r="B223" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C223">
         <v>0</v>
       </c>
       <c r="D223" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.35">
@@ -3561,13 +3558,13 @@
         <v>75</v>
       </c>
       <c r="B224" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.35">
@@ -3575,13 +3572,13 @@
         <v>75</v>
       </c>
       <c r="B225" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C225">
         <v>0</v>
       </c>
       <c r="D225" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.35">
@@ -3589,13 +3586,13 @@
         <v>75</v>
       </c>
       <c r="B226" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C226">
         <v>0</v>
       </c>
       <c r="D226" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.35">
@@ -3603,13 +3600,13 @@
         <v>76</v>
       </c>
       <c r="B227" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C227">
         <v>0</v>
       </c>
       <c r="D227" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.35">
@@ -3617,13 +3614,13 @@
         <v>76</v>
       </c>
       <c r="B228" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.35">
@@ -3631,13 +3628,13 @@
         <v>76</v>
       </c>
       <c r="B229" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C229">
         <v>0</v>
       </c>
       <c r="D229" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.35">
@@ -3645,13 +3642,13 @@
         <v>77</v>
       </c>
       <c r="B230" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.35">
@@ -3659,13 +3656,13 @@
         <v>77</v>
       </c>
       <c r="B231" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C231">
         <v>0</v>
       </c>
       <c r="D231" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.35">
@@ -3673,13 +3670,13 @@
         <v>77</v>
       </c>
       <c r="B232" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C232">
         <v>0</v>
       </c>
       <c r="D232" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.35">
@@ -3687,13 +3684,13 @@
         <v>78</v>
       </c>
       <c r="B233" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.35">
@@ -3701,13 +3698,13 @@
         <v>78</v>
       </c>
       <c r="B234" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C234">
         <v>0</v>
       </c>
       <c r="D234" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.35">
@@ -3715,13 +3712,13 @@
         <v>78</v>
       </c>
       <c r="B235" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C235">
         <v>0</v>
       </c>
       <c r="D235" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.35">
@@ -3729,13 +3726,13 @@
         <v>79</v>
       </c>
       <c r="B236" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.35">
@@ -3743,13 +3740,13 @@
         <v>79</v>
       </c>
       <c r="B237" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C237">
         <v>0</v>
       </c>
       <c r="D237" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.35">
@@ -3757,13 +3754,13 @@
         <v>79</v>
       </c>
       <c r="B238" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C238">
         <v>0</v>
       </c>
       <c r="D238" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.35">
@@ -3771,13 +3768,13 @@
         <v>80</v>
       </c>
       <c r="B239" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C239">
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.35">
@@ -3785,13 +3782,13 @@
         <v>80</v>
       </c>
       <c r="B240" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C240">
         <v>0</v>
       </c>
       <c r="D240" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.35">
@@ -3799,13 +3796,13 @@
         <v>80</v>
       </c>
       <c r="B241" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C241">
         <v>0</v>
       </c>
       <c r="D241" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.35">
@@ -3813,13 +3810,13 @@
         <v>81</v>
       </c>
       <c r="B242" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C242">
         <v>1</v>
       </c>
       <c r="D242" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.35">
@@ -3827,13 +3824,13 @@
         <v>81</v>
       </c>
       <c r="B243" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C243">
         <v>0</v>
       </c>
       <c r="D243" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.35">
@@ -3841,13 +3838,13 @@
         <v>81</v>
       </c>
       <c r="B244" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C244">
         <v>0</v>
       </c>
       <c r="D244" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.35">
@@ -3855,13 +3852,13 @@
         <v>82</v>
       </c>
       <c r="B245" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C245">
         <v>0</v>
       </c>
       <c r="D245" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.35">
@@ -3869,13 +3866,13 @@
         <v>82</v>
       </c>
       <c r="B246" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.35">
@@ -3883,13 +3880,13 @@
         <v>82</v>
       </c>
       <c r="B247" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C247">
         <v>0</v>
       </c>
       <c r="D247" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.35">
@@ -3897,13 +3894,13 @@
         <v>83</v>
       </c>
       <c r="B248" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C248">
         <v>0</v>
       </c>
       <c r="D248" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.35">
@@ -3911,13 +3908,13 @@
         <v>83</v>
       </c>
       <c r="B249" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C249">
         <v>0</v>
       </c>
       <c r="D249" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.35">
@@ -3925,13 +3922,13 @@
         <v>83</v>
       </c>
       <c r="B250" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.35">
@@ -3939,13 +3936,13 @@
         <v>84</v>
       </c>
       <c r="B251" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C251">
         <v>0</v>
       </c>
       <c r="D251" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.35">
@@ -3953,13 +3950,13 @@
         <v>84</v>
       </c>
       <c r="B252" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.35">
@@ -3967,13 +3964,13 @@
         <v>84</v>
       </c>
       <c r="B253" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C253">
         <v>0</v>
       </c>
       <c r="D253" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.35">
@@ -3981,13 +3978,13 @@
         <v>85</v>
       </c>
       <c r="B254" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.35">
@@ -3995,13 +3992,13 @@
         <v>85</v>
       </c>
       <c r="B255" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C255">
         <v>0</v>
       </c>
       <c r="D255" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.35">
@@ -4009,13 +4006,13 @@
         <v>85</v>
       </c>
       <c r="B256" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C256">
         <v>0</v>
       </c>
       <c r="D256" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.35">
@@ -4023,13 +4020,13 @@
         <v>86</v>
       </c>
       <c r="B257" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C257">
         <v>1</v>
       </c>
       <c r="D257" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.35">
@@ -4037,13 +4034,13 @@
         <v>86</v>
       </c>
       <c r="B258" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C258">
         <v>0</v>
       </c>
       <c r="D258" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.35">
@@ -4051,13 +4048,13 @@
         <v>86</v>
       </c>
       <c r="B259" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C259">
         <v>0</v>
       </c>
       <c r="D259" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.35">
@@ -4065,13 +4062,13 @@
         <v>87</v>
       </c>
       <c r="B260" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C260">
         <v>0</v>
       </c>
       <c r="D260" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.35">
@@ -4079,13 +4076,13 @@
         <v>87</v>
       </c>
       <c r="B261" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.35">
@@ -4093,13 +4090,13 @@
         <v>87</v>
       </c>
       <c r="B262" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C262">
         <v>0</v>
       </c>
       <c r="D262" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.35">
@@ -4107,13 +4104,13 @@
         <v>88</v>
       </c>
       <c r="B263" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C263">
         <v>0</v>
       </c>
       <c r="D263" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.35">
@@ -4121,13 +4118,13 @@
         <v>88</v>
       </c>
       <c r="B264" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C264">
         <v>0</v>
       </c>
       <c r="D264" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.35">
@@ -4135,13 +4132,13 @@
         <v>88</v>
       </c>
       <c r="B265" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.35">
@@ -4149,13 +4146,13 @@
         <v>89</v>
       </c>
       <c r="B266" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C266">
         <v>0</v>
       </c>
       <c r="D266" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.35">
@@ -4163,13 +4160,13 @@
         <v>89</v>
       </c>
       <c r="B267" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C267">
         <v>1</v>
       </c>
       <c r="D267" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.35">
@@ -4177,13 +4174,13 @@
         <v>89</v>
       </c>
       <c r="B268" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C268">
         <v>0</v>
       </c>
       <c r="D268" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.35">
@@ -4191,13 +4188,13 @@
         <v>90</v>
       </c>
       <c r="B269" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C269">
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.35">
@@ -4205,13 +4202,13 @@
         <v>90</v>
       </c>
       <c r="B270" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C270">
         <v>0</v>
       </c>
       <c r="D270" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.35">
@@ -4219,13 +4216,13 @@
         <v>90</v>
       </c>
       <c r="B271" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C271">
         <v>0</v>
       </c>
       <c r="D271" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.35">
@@ -4233,13 +4230,13 @@
         <v>91</v>
       </c>
       <c r="B272" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C272">
         <v>0</v>
       </c>
       <c r="D272" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.35">
@@ -4247,13 +4244,13 @@
         <v>91</v>
       </c>
       <c r="B273" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C273">
         <v>0</v>
       </c>
       <c r="D273" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.35">
@@ -4261,13 +4258,13 @@
         <v>91</v>
       </c>
       <c r="B274" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.35">
@@ -4275,13 +4272,13 @@
         <v>92</v>
       </c>
       <c r="B275" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C275">
         <v>1</v>
       </c>
       <c r="D275" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.35">
@@ -4289,13 +4286,13 @@
         <v>92</v>
       </c>
       <c r="B276" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C276">
         <v>0</v>
       </c>
       <c r="D276" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.35">
@@ -4303,13 +4300,13 @@
         <v>92</v>
       </c>
       <c r="B277" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C277">
         <v>0</v>
       </c>
       <c r="D277" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.35">
@@ -4317,13 +4314,13 @@
         <v>93</v>
       </c>
       <c r="B278" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.35">
@@ -4331,13 +4328,13 @@
         <v>93</v>
       </c>
       <c r="B279" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C279">
         <v>0</v>
       </c>
       <c r="D279" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.35">
@@ -4345,13 +4342,13 @@
         <v>93</v>
       </c>
       <c r="B280" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C280">
         <v>0</v>
       </c>
       <c r="D280" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.35">
@@ -4359,13 +4356,13 @@
         <v>94</v>
       </c>
       <c r="B281" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.35">
@@ -4373,13 +4370,13 @@
         <v>94</v>
       </c>
       <c r="B282" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C282">
         <v>0</v>
       </c>
       <c r="D282" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.35">
@@ -4387,13 +4384,13 @@
         <v>94</v>
       </c>
       <c r="B283" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C283">
         <v>0</v>
       </c>
       <c r="D283" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.35">
@@ -4401,13 +4398,13 @@
         <v>95</v>
       </c>
       <c r="B284" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.35">
@@ -4415,13 +4412,13 @@
         <v>95</v>
       </c>
       <c r="B285" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C285">
         <v>0</v>
       </c>
       <c r="D285" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.35">
@@ -4429,13 +4426,13 @@
         <v>95</v>
       </c>
       <c r="B286" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C286">
         <v>0</v>
       </c>
       <c r="D286" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.35">
@@ -4443,13 +4440,13 @@
         <v>96</v>
       </c>
       <c r="B287" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C287">
         <v>1</v>
       </c>
       <c r="D287" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.35">
@@ -4457,13 +4454,13 @@
         <v>96</v>
       </c>
       <c r="B288" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C288">
         <v>0</v>
       </c>
       <c r="D288" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.35">
@@ -4471,13 +4468,13 @@
         <v>96</v>
       </c>
       <c r="B289" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C289">
         <v>0</v>
       </c>
       <c r="D289" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.35">
@@ -4485,13 +4482,13 @@
         <v>97</v>
       </c>
       <c r="B290" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.35">
@@ -4499,13 +4496,13 @@
         <v>97</v>
       </c>
       <c r="B291" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C291">
         <v>0</v>
       </c>
       <c r="D291" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.35">
@@ -4513,13 +4510,13 @@
         <v>97</v>
       </c>
       <c r="B292" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C292">
         <v>0</v>
       </c>
       <c r="D292" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.35">
@@ -4527,13 +4524,13 @@
         <v>98</v>
       </c>
       <c r="B293" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.35">
@@ -4541,13 +4538,13 @@
         <v>98</v>
       </c>
       <c r="B294" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C294">
         <v>0</v>
       </c>
       <c r="D294" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.35">
@@ -4555,13 +4552,13 @@
         <v>98</v>
       </c>
       <c r="B295" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C295">
         <v>0</v>
       </c>
       <c r="D295" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.35">
@@ -4569,13 +4566,13 @@
         <v>99</v>
       </c>
       <c r="B296" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C296">
         <v>0</v>
       </c>
       <c r="D296" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.35">
@@ -4583,13 +4580,13 @@
         <v>99</v>
       </c>
       <c r="B297" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.35">
@@ -4597,13 +4594,13 @@
         <v>99</v>
       </c>
       <c r="B298" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C298">
         <v>0</v>
       </c>
       <c r="D298" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.35">
@@ -4611,13 +4608,13 @@
         <v>100</v>
       </c>
       <c r="B299" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.35">
@@ -4625,13 +4622,13 @@
         <v>100</v>
       </c>
       <c r="B300" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C300">
         <v>0</v>
       </c>
       <c r="D300" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.35">
@@ -4639,13 +4636,13 @@
         <v>100</v>
       </c>
       <c r="B301" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C301">
         <v>0</v>
       </c>
       <c r="D301" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
